--- a/slides/vol-22/downloads/pa45-vol22-survey.xlsx
+++ b/slides/vol-22/downloads/pa45-vol22-survey.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="アンケート" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expenses" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -129,14 +125,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="アンケート" displayName="アンケート" ref="A1:C6" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ExpenseTable" displayName="ExpenseTable" ref="A1:C6" headerRowCount="1">
   <autoFilter ref="A1:C6"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="名前"/>
-    <tableColumn id="2" name="満足度"/>
-    <tableColumn id="3" name="コメント"/>
+    <tableColumn id="1" name="Name"/>
+    <tableColumn id="2" name="Amount"/>
+    <tableColumn id="3" name="Date"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -432,100 +428,100 @@
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>名前</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>満足度</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>コメント</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Date</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>山田 太郎</t>
+          <t>Tanaka</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>3000</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>とても分かりやすかった</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>佐藤 花子</t>
+          <t>Suzuki</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>15000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>また参加したい</t>
+          <t>2026-04-01</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>鈴木 一郎</t>
+          <t>Sato</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>8000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>実演が参考になった</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>田中 みか</t>
+          <t>Yamada</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>25000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>資料が丁寧</t>
+          <t>2026-04-02</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>高橋 健</t>
+          <t>Ito</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>1200</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>45分でちょうど良い</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
